--- a/Digital-Business-Toolkit/03-Quote/Product.xlsx
+++ b/Digital-Business-Toolkit/03-Quote/Product.xlsx
@@ -7,11 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Main Workspace" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Quote Summary" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Quick Start" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="User Guide" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="לוח בקרה" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="שולחן עבודה" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="סיכום הצעות מחיר" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="התחלה מהירה" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="מדריך שימוש" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -652,7 +652,7 @@
     <row r="2" ht="46" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Smart Quote Builder — Dashboard</t>
+          <t>לוח בקרה — בניית הצעות מחיר</t>
         </is>
       </c>
       <c r="C2" s="2" t="n"/>
@@ -663,7 +663,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>ContractorOS — Send professional quotes, close more jobs</t>
+          <t>ContractorOS — שלחו הצעות מקצועיות וסגרו יותר עבודות</t>
         </is>
       </c>
       <c r="C3" s="4" t="n"/>
@@ -700,42 +700,42 @@
     </row>
     <row r="6" ht="34" customHeight="1">
       <c r="B6" s="6">
-        <f>COUNTA('Quote Summary'!A4:A25)</f>
+        <f>COUNTA('סיכום הצעות מחיר'!A4:A25)</f>
         <v/>
       </c>
       <c r="C6" s="6">
-        <f>SUM('Quote Summary'!H4:H25)</f>
+        <f>SUM('סיכום הצעות מחיר'!H4:H25)</f>
         <v/>
       </c>
       <c r="D6" s="6">
-        <f>COUNTIF('Quote Summary'!I4:I25,"אושרה")</f>
+        <f>COUNTIF('סיכום הצעות מחיר'!I4:I25,"אושרה")</f>
         <v/>
       </c>
       <c r="E6" s="7">
-        <f>IFERROR(COUNTIF('Quote Summary'!I4:I25,"אושרה")/COUNTA('Quote Summary'!A4:A25),0)</f>
+        <f>IFERROR(COUNTIF('סיכום הצעות מחיר'!I4:I25,"אושרה")/COUNTA('סיכום הצעות מחיר'!A4:A25),0)</f>
         <v/>
       </c>
       <c r="F6" s="6">
-        <f>IFERROR(AVERAGE('Quote Summary'!H4:H25),0)</f>
+        <f>IFERROR(AVERAGE('סיכום הצעות מחיר'!H4:H25),0)</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>⚠ Business Insights / התראות</t>
+          <t>⚠ תובנות עסקיות והתראות</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="B10" s="9">
-        <f>IF(COUNTIF('Quote Summary'!I4:I25,"טיוטה")&gt;0,"יש "&amp;COUNTIF('Quote Summary'!I4:I25,"טיוטה")&amp;" הצעות בטיוטה שטרם נשלחו.","כל ההצעות נשלחו ללקוחות.")</f>
+        <f>IF(COUNTIF('סיכום הצעות מחיר'!I4:I25,"טיוטה")&gt;0,"יש "&amp;COUNTIF('סיכום הצעות מחיר'!I4:I25,"טיוטה")&amp;" הצעות בטיוטה שטרם נשלחו.","כל ההצעות נשלחו ללקוחות.")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="B11" s="10">
-        <f>IF(COUNTA('Quote Summary'!A4:A25)=0,"עדיין לא הוזנו הצעות מחיר.","נתוני ההצעות מתעדכנים אוטומטית מהלשונית Main Workspace.")</f>
+        <f>IF(COUNTA('סיכום הצעות מחיר'!A4:A25)=0,"עדיין לא הוזנו הצעות מחיר.","נתוני ההצעות מתעדכנים אוטומטית מהלשונית שולחן עבודה.")</f>
         <v/>
       </c>
     </row>
@@ -777,7 +777,7 @@
     <row r="1" ht="44" customHeight="1">
       <c r="A1" s="11" t="inlineStr">
         <is>
-          <t>בניית הצעת מחיר | Smart Quote Builder — סעיפי הצעה</t>
+          <t>בניית הצעת מחיר - סעיפי הצעה</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -821,7 +821,7 @@
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>פרויקט</t>
+          <t>שם פרויקט</t>
         </is>
       </c>
       <c r="D3" s="12" t="inlineStr">
@@ -1608,7 +1608,7 @@
     <row r="1" ht="44" customHeight="1">
       <c r="A1" s="11" t="inlineStr">
         <is>
-          <t>סיכום הצעות מחיר | Quote Summary</t>
+          <t>סיכום הצעות מחיר</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1623,7 +1623,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>שורה אחת לכל מספר הצעה — הסכומים נשאבים אוטומטית מ-Main Workspace</t>
+          <t>שורה אחת לכל מספר הצעה — הסכומים נשאבים אוטומטית מ-שולחן עבודה</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -1705,7 +1705,7 @@
         <v>0.17</v>
       </c>
       <c r="F4" s="21">
-        <f>SUMIF('Main Workspace'!$A$4:$A$38,A4,'Main Workspace'!$J$4:$J$38)</f>
+        <f>SUMIF('שולחן עבודה'!$A$4:$A$38,A4,'שולחן עבודה'!$J$4:$J$38)</f>
         <v/>
       </c>
       <c r="G4" s="21">
@@ -1745,7 +1745,7 @@
         <v>0.17</v>
       </c>
       <c r="F5" s="21">
-        <f>SUMIF('Main Workspace'!$A$4:$A$38,A5,'Main Workspace'!$J$4:$J$38)</f>
+        <f>SUMIF('שולחן עבודה'!$A$4:$A$38,A5,'שולחן עבודה'!$J$4:$J$38)</f>
         <v/>
       </c>
       <c r="G5" s="21">
@@ -1769,7 +1769,7 @@
       <c r="D6" s="18" t="n"/>
       <c r="E6" s="20" t="n"/>
       <c r="F6" s="21">
-        <f>IF(A6="","",SUMIF('Main Workspace'!$A$4:$A$38,A6,'Main Workspace'!$J$4:$J$38))</f>
+        <f>IF(A6="","",SUMIF('שולחן עבודה'!$A$4:$A$38,A6,'שולחן עבודה'!$J$4:$J$38))</f>
         <v/>
       </c>
       <c r="G6" s="21">
@@ -1789,7 +1789,7 @@
       <c r="D7" s="18" t="n"/>
       <c r="E7" s="20" t="n"/>
       <c r="F7" s="21">
-        <f>IF(A7="","",SUMIF('Main Workspace'!$A$4:$A$38,A7,'Main Workspace'!$J$4:$J$38))</f>
+        <f>IF(A7="","",SUMIF('שולחן עבודה'!$A$4:$A$38,A7,'שולחן עבודה'!$J$4:$J$38))</f>
         <v/>
       </c>
       <c r="G7" s="21">
@@ -1809,7 +1809,7 @@
       <c r="D8" s="18" t="n"/>
       <c r="E8" s="20" t="n"/>
       <c r="F8" s="21">
-        <f>IF(A8="","",SUMIF('Main Workspace'!$A$4:$A$38,A8,'Main Workspace'!$J$4:$J$38))</f>
+        <f>IF(A8="","",SUMIF('שולחן עבודה'!$A$4:$A$38,A8,'שולחן עבודה'!$J$4:$J$38))</f>
         <v/>
       </c>
       <c r="G8" s="21">
@@ -1829,7 +1829,7 @@
       <c r="D9" s="18" t="n"/>
       <c r="E9" s="20" t="n"/>
       <c r="F9" s="21">
-        <f>IF(A9="","",SUMIF('Main Workspace'!$A$4:$A$38,A9,'Main Workspace'!$J$4:$J$38))</f>
+        <f>IF(A9="","",SUMIF('שולחן עבודה'!$A$4:$A$38,A9,'שולחן עבודה'!$J$4:$J$38))</f>
         <v/>
       </c>
       <c r="G9" s="21">
@@ -1849,7 +1849,7 @@
       <c r="D10" s="18" t="n"/>
       <c r="E10" s="20" t="n"/>
       <c r="F10" s="21">
-        <f>IF(A10="","",SUMIF('Main Workspace'!$A$4:$A$38,A10,'Main Workspace'!$J$4:$J$38))</f>
+        <f>IF(A10="","",SUMIF('שולחן עבודה'!$A$4:$A$38,A10,'שולחן עבודה'!$J$4:$J$38))</f>
         <v/>
       </c>
       <c r="G10" s="21">
@@ -1869,7 +1869,7 @@
       <c r="D11" s="18" t="n"/>
       <c r="E11" s="20" t="n"/>
       <c r="F11" s="21">
-        <f>IF(A11="","",SUMIF('Main Workspace'!$A$4:$A$38,A11,'Main Workspace'!$J$4:$J$38))</f>
+        <f>IF(A11="","",SUMIF('שולחן עבודה'!$A$4:$A$38,A11,'שולחן עבודה'!$J$4:$J$38))</f>
         <v/>
       </c>
       <c r="G11" s="21">
@@ -1889,7 +1889,7 @@
       <c r="D12" s="18" t="n"/>
       <c r="E12" s="20" t="n"/>
       <c r="F12" s="21">
-        <f>IF(A12="","",SUMIF('Main Workspace'!$A$4:$A$38,A12,'Main Workspace'!$J$4:$J$38))</f>
+        <f>IF(A12="","",SUMIF('שולחן עבודה'!$A$4:$A$38,A12,'שולחן עבודה'!$J$4:$J$38))</f>
         <v/>
       </c>
       <c r="G12" s="21">
@@ -1909,7 +1909,7 @@
       <c r="D13" s="18" t="n"/>
       <c r="E13" s="20" t="n"/>
       <c r="F13" s="21">
-        <f>IF(A13="","",SUMIF('Main Workspace'!$A$4:$A$38,A13,'Main Workspace'!$J$4:$J$38))</f>
+        <f>IF(A13="","",SUMIF('שולחן עבודה'!$A$4:$A$38,A13,'שולחן עבודה'!$J$4:$J$38))</f>
         <v/>
       </c>
       <c r="G13" s="21">
@@ -1929,7 +1929,7 @@
       <c r="D14" s="18" t="n"/>
       <c r="E14" s="20" t="n"/>
       <c r="F14" s="21">
-        <f>IF(A14="","",SUMIF('Main Workspace'!$A$4:$A$38,A14,'Main Workspace'!$J$4:$J$38))</f>
+        <f>IF(A14="","",SUMIF('שולחן עבודה'!$A$4:$A$38,A14,'שולחן עבודה'!$J$4:$J$38))</f>
         <v/>
       </c>
       <c r="G14" s="21">
@@ -1949,7 +1949,7 @@
       <c r="D15" s="18" t="n"/>
       <c r="E15" s="20" t="n"/>
       <c r="F15" s="21">
-        <f>IF(A15="","",SUMIF('Main Workspace'!$A$4:$A$38,A15,'Main Workspace'!$J$4:$J$38))</f>
+        <f>IF(A15="","",SUMIF('שולחן עבודה'!$A$4:$A$38,A15,'שולחן עבודה'!$J$4:$J$38))</f>
         <v/>
       </c>
       <c r="G15" s="21">
@@ -1969,7 +1969,7 @@
       <c r="D16" s="18" t="n"/>
       <c r="E16" s="20" t="n"/>
       <c r="F16" s="21">
-        <f>IF(A16="","",SUMIF('Main Workspace'!$A$4:$A$38,A16,'Main Workspace'!$J$4:$J$38))</f>
+        <f>IF(A16="","",SUMIF('שולחן עבודה'!$A$4:$A$38,A16,'שולחן עבודה'!$J$4:$J$38))</f>
         <v/>
       </c>
       <c r="G16" s="21">
@@ -1989,7 +1989,7 @@
       <c r="D17" s="18" t="n"/>
       <c r="E17" s="20" t="n"/>
       <c r="F17" s="21">
-        <f>IF(A17="","",SUMIF('Main Workspace'!$A$4:$A$38,A17,'Main Workspace'!$J$4:$J$38))</f>
+        <f>IF(A17="","",SUMIF('שולחן עבודה'!$A$4:$A$38,A17,'שולחן עבודה'!$J$4:$J$38))</f>
         <v/>
       </c>
       <c r="G17" s="21">
@@ -2009,7 +2009,7 @@
       <c r="D18" s="18" t="n"/>
       <c r="E18" s="20" t="n"/>
       <c r="F18" s="21">
-        <f>IF(A18="","",SUMIF('Main Workspace'!$A$4:$A$38,A18,'Main Workspace'!$J$4:$J$38))</f>
+        <f>IF(A18="","",SUMIF('שולחן עבודה'!$A$4:$A$38,A18,'שולחן עבודה'!$J$4:$J$38))</f>
         <v/>
       </c>
       <c r="G18" s="21">
@@ -2029,7 +2029,7 @@
       <c r="D19" s="18" t="n"/>
       <c r="E19" s="20" t="n"/>
       <c r="F19" s="21">
-        <f>IF(A19="","",SUMIF('Main Workspace'!$A$4:$A$38,A19,'Main Workspace'!$J$4:$J$38))</f>
+        <f>IF(A19="","",SUMIF('שולחן עבודה'!$A$4:$A$38,A19,'שולחן עבודה'!$J$4:$J$38))</f>
         <v/>
       </c>
       <c r="G19" s="21">
@@ -2049,7 +2049,7 @@
       <c r="D20" s="18" t="n"/>
       <c r="E20" s="20" t="n"/>
       <c r="F20" s="21">
-        <f>IF(A20="","",SUMIF('Main Workspace'!$A$4:$A$38,A20,'Main Workspace'!$J$4:$J$38))</f>
+        <f>IF(A20="","",SUMIF('שולחן עבודה'!$A$4:$A$38,A20,'שולחן עבודה'!$J$4:$J$38))</f>
         <v/>
       </c>
       <c r="G20" s="21">
@@ -2069,7 +2069,7 @@
       <c r="D21" s="18" t="n"/>
       <c r="E21" s="20" t="n"/>
       <c r="F21" s="21">
-        <f>IF(A21="","",SUMIF('Main Workspace'!$A$4:$A$38,A21,'Main Workspace'!$J$4:$J$38))</f>
+        <f>IF(A21="","",SUMIF('שולחן עבודה'!$A$4:$A$38,A21,'שולחן עבודה'!$J$4:$J$38))</f>
         <v/>
       </c>
       <c r="G21" s="21">
@@ -2089,7 +2089,7 @@
       <c r="D22" s="18" t="n"/>
       <c r="E22" s="20" t="n"/>
       <c r="F22" s="21">
-        <f>IF(A22="","",SUMIF('Main Workspace'!$A$4:$A$38,A22,'Main Workspace'!$J$4:$J$38))</f>
+        <f>IF(A22="","",SUMIF('שולחן עבודה'!$A$4:$A$38,A22,'שולחן עבודה'!$J$4:$J$38))</f>
         <v/>
       </c>
       <c r="G22" s="21">
@@ -2109,7 +2109,7 @@
       <c r="D23" s="18" t="n"/>
       <c r="E23" s="20" t="n"/>
       <c r="F23" s="21">
-        <f>IF(A23="","",SUMIF('Main Workspace'!$A$4:$A$38,A23,'Main Workspace'!$J$4:$J$38))</f>
+        <f>IF(A23="","",SUMIF('שולחן עבודה'!$A$4:$A$38,A23,'שולחן עבודה'!$J$4:$J$38))</f>
         <v/>
       </c>
       <c r="G23" s="21">
@@ -2129,7 +2129,7 @@
       <c r="D24" s="18" t="n"/>
       <c r="E24" s="20" t="n"/>
       <c r="F24" s="21">
-        <f>IF(A24="","",SUMIF('Main Workspace'!$A$4:$A$38,A24,'Main Workspace'!$J$4:$J$38))</f>
+        <f>IF(A24="","",SUMIF('שולחן עבודה'!$A$4:$A$38,A24,'שולחן עבודה'!$J$4:$J$38))</f>
         <v/>
       </c>
       <c r="G24" s="21">
@@ -2149,7 +2149,7 @@
       <c r="D25" s="18" t="n"/>
       <c r="E25" s="20" t="n"/>
       <c r="F25" s="21">
-        <f>IF(A25="","",SUMIF('Main Workspace'!$A$4:$A$38,A25,'Main Workspace'!$J$4:$J$38))</f>
+        <f>IF(A25="","",SUMIF('שולחן עבודה'!$A$4:$A$38,A25,'שולחן עבודה'!$J$4:$J$38))</f>
         <v/>
       </c>
       <c r="G25" s="21">
@@ -2204,7 +2204,7 @@
     <row r="1" ht="44" customHeight="1">
       <c r="A1" s="11" t="inlineStr">
         <is>
-          <t>התחלה מהירה | Quick Start</t>
+          <t>התחלה מהירה</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2220,21 +2220,21 @@
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="24" t="inlineStr">
         <is>
-          <t>1. עברו ללשונית 'Main Workspace' והוסיפו סעיף (שורה) לכל פריט עבודה, עם אותו מספר הצעה לכל הסעיפים של אותה הצעה.</t>
+          <t>1. עברו ללשונית 'שולחן עבודה' והוסיפו סעיף (שורה) לכל פריט עבודה, עם אותו מספר הצעה לכל הסעיפים של אותה הצעה.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
         <is>
-          <t>2. עברו ללשונית 'Quote Summary' והוסיפו שורה אחת לכל מספר הצעה, עם תוקף, תנאי תשלום ומע"מ.</t>
+          <t>2. עברו ללשונית 'סיכום הצעות מחיר' והוסיפו שורה אחת לכל מספר הצעה, עם תוקף, תנאי תשלום ומע"מ.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1">
       <c r="A8" s="24" t="inlineStr">
         <is>
-          <t>3. הסכומים (לפני מע"מ, מע"מ, כולל מע"מ) מחושבים אוטומטית משורות ה-Main Workspace.</t>
+          <t>3. הסכומים (לפני מע"מ, מע"מ, כולל מע"מ) מחושבים אוטומטית משורות ה-שולחן עבודה.</t>
         </is>
       </c>
     </row>
@@ -2248,14 +2248,14 @@
     <row r="12" ht="34" customHeight="1">
       <c r="A12" s="24" t="inlineStr">
         <is>
-          <t>5. עברו ל-Dashboard לראות כמה הצעות פתוחות, כמה אושרו, ומה שווי הצינור הכולל.</t>
+          <t>5. עברו ל-לוח הבקרה לראות כמה הצעות פתוחות, כמה אושרו, ומה שווי הצינור הכולל.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="40" customHeight="1">
       <c r="A14" s="25" t="inlineStr">
         <is>
-          <t>טיפ: להדפסה נוחה ללקוח, סננו את Main Workspace לפי מספר הצעה יחיד לפני הדפסה/PDF.</t>
+          <t>טיפ: להדפסה נוחה ללקוח, סננו את שולחן עבודה לפי מספר הצעה יחיד לפני הדפסה/PDF.</t>
         </is>
       </c>
     </row>
@@ -2292,7 +2292,7 @@
     <row r="1" ht="44" customHeight="1">
       <c r="A1" s="11" t="inlineStr">
         <is>
-          <t>מדריך שימוש | User Guide</t>
+          <t>מדריך שימוש</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="C7" s="27" t="inlineStr">
         <is>
-          <t>הוסיפו סעיפי עבודה ב-Main Workspace, ופרטי הצעה כלליים ב-Quote Summary.</t>
+          <t>הוסיפו סעיפי עבודה ב-שולחן עבודה, ופרטי הצעה כלליים בסיכום הצעות מחיר.</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
     <row r="10" ht="46" customHeight="1">
       <c r="B10" s="26" t="inlineStr">
         <is>
-          <t>מה Dashboard מציג?</t>
+          <t>מה לוח הבקרה מציג?</t>
         </is>
       </c>
       <c r="C10" s="27" t="inlineStr">
@@ -2399,14 +2399,14 @@
       </c>
       <c r="C11" s="27" t="inlineStr">
         <is>
-          <t>1) שמרו על מספור הצעות עקבי (Q-1001, Q-1002...). 2) עדכנו סטטוס בכל שלב כדי שה-Dashboard ישקף מצב אמיתי.</t>
+          <t>1) שמרו על מספור הצעות עקבי (Q-1001, Q-1002...). 2) עדכנו סטטוס בכל שלב כדי שלוח הבקרה ישקף מצב אמיתי.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="28" t="inlineStr">
         <is>
-          <t>שאלות נפוצות (FAQ)</t>
+          <t>שאלות נפוצות</t>
         </is>
       </c>
     </row>
@@ -2418,7 +2418,7 @@
       </c>
       <c r="C14" s="27" t="inlineStr">
         <is>
-          <t>סננו את Main Workspace לפי מספר הצעה בודד, ואת Quote Summary לאותה שורה, והדפיסו/ייצאו כ-PDF (Excel: File &gt; Export &gt; Create PDF).</t>
+          <t>סננו את שולחן עבודה לפי מספר הצעה בודד, ואת סיכום הצעות מחיר לאותה שורה, והדפיסו/ייצאו כ-PDF (Excel: File &gt; Export &gt; Create PDF).</t>
         </is>
       </c>
     </row>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="C15" s="27" t="inlineStr">
         <is>
-          <t>כן — הוסיפו שורה חדשה ב-Main Workspace עם אותו מספר הצעה.</t>
+          <t>כן — הוסיפו שורה חדשה ב-שולחן עבודה עם אותו מספר הצעה.</t>
         </is>
       </c>
     </row>

--- a/Digital-Business-Toolkit/03-Quote/Product.xlsx
+++ b/Digital-Business-Toolkit/03-Quote/Product.xlsx
@@ -663,7 +663,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>ContractorOS — שלחו הצעות מקצועיות וסגרו יותר עבודות</t>
+          <t>JobMargin — שלחו הצעות מקצועיות וסגרו יותר עבודות</t>
         </is>
       </c>
       <c r="C3" s="4" t="n"/>
